--- a/event_registration_forms/022_pajama_party_registration--event_registration_forms.xlsx
+++ b/event_registration_forms/022_pajama_party_registration--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -870,29 +870,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pajama_party_hat</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pajama Party Hat</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pajama_clad_choices_choices</t>
+          <t>pajama_party_time_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>6:00_am</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>6:00 AM</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6:00_am</t>
+          <t>7:00_am</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6:00 AM</t>
+          <t>7:00 AM</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7:00_am</t>
+          <t>8:00_am</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7:00 AM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8:00_am</t>
+          <t>9:00_am</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9:00_am</t>
+          <t>10:00_am</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00_am</t>
+          <t>11:00_am</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00_am</t>
+          <t>12:00_pm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1006,29 +1006,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00_pm</t>
+          <t>1:00_pm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pajama_party_time_choices</t>
+          <t>event_venue_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1:00_pm</t>
+          <t>school_hall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>School Hall</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_hall</t>
+          <t>community_center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>School Hall</t>
+          <t>Community Center</t>
         </is>
       </c>
     </row>
@@ -1057,29 +1057,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>community_center</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Community Center</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>event_venue_choices</t>
+          <t>event_organizer_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1108,27 +1108,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>event_organizer_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
